--- a/results/reliability_eval/Llama-3-8B_P159_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P159_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5994193137826801</v>
+        <v>0.4785559794728499</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7112645489191052</v>
+        <v>0.1801997773554012</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5994193137826801</v>
+        <v>0.4785559794728499</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7112645489191052</v>
+        <v>0.1801997773554012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3830275229357798</v>
+        <v>0.5244733872484484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5836330430344706</v>
+        <v>0.2676215247701658</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9994166622474412</v>
+        <v>0.9999462640049437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9995990889781515</v>
+        <v>0.9995373048004627</v>
       </c>
       <c r="I2" t="n">
-        <v>0.654</v>
+        <v>0.182</v>
       </c>
     </row>
   </sheetData>
